--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -474,7 +474,7 @@
     <t>lead</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_NumberOfLead}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_NumberOfLead|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -494,7 +494,7 @@
     <t>deviceInterpretation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_DeviceInterpretation}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_DeviceInterpretation|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -510,7 +510,7 @@
     <t>duration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_Duration}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_Duration|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -526,7 +526,7 @@
     <t>stressType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_StressType}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_StressType|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -592,7 +592,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -618,7 +618,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|1.3.0-dev|MedicationStatement|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|1.3.0-dev|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -720,7 +720,7 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|1.1.0</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -1029,7 +1029,7 @@
     <t>心電図検査について、負荷試験などの条件をつけた分類</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>Observation.category:third.id</t>
@@ -1099,7 +1099,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1123,7 +1123,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Group|Device|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Group|4.0.1|Device|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1151,7 +1151,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1171,7 +1171,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1253,7 +1253,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1328,7 +1328,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1357,7 +1357,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1718,7 +1718,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1748,7 +1748,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1760,7 +1760,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1785,7 +1785,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1860,7 +1860,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1910,7 +1910,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1943,7 +1943,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1980,7 +1980,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1999,7 +1999,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -2051,7 +2051,7 @@
     <t>心電図の各検査項目についてはLOINCなどの特定の用語集を利用することが推奨される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2701,7 +2701,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.1875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="77.1796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -474,7 +474,7 @@
     <t>lead</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_NumberOfLead|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_NumberOfLead}
 </t>
   </si>
   <si>
@@ -494,7 +494,7 @@
     <t>deviceInterpretation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_DeviceInterpretation|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_DeviceInterpretation}
 </t>
   </si>
   <si>
@@ -510,7 +510,7 @@
     <t>duration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_Duration|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_Duration}
 </t>
   </si>
   <si>
@@ -526,7 +526,7 @@
     <t>stressType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_StressType|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_StressType}
 </t>
   </si>
   <si>
@@ -592,7 +592,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -618,7 +618,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|1.3.0-dev|MedicationStatement|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|1.3.0-dev|ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -720,7 +720,7 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -1029,7 +1029,7 @@
     <t>心電図検査について、負荷試験などの条件をつけた分類</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:third.id</t>
@@ -1099,7 +1099,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1123,7 +1123,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Group|4.0.1|Device|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Group|Device|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -1151,7 +1151,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1171,7 +1171,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1253,7 +1253,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1328,7 +1328,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1357,7 +1357,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1718,7 +1718,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1748,7 +1748,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1760,7 +1760,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>
@@ -1785,7 +1785,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1860,7 +1860,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1910,7 +1910,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1943,7 +1943,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1980,7 +1980,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence)
 </t>
   </si>
   <si>
@@ -1999,7 +1999,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|MolecularSequence)
 </t>
   </si>
   <si>
@@ -2051,7 +2051,7 @@
     <t>心電図の各検査項目についてはLOINCなどの特定の用語集を利用することが推奨される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2701,7 +2701,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.1796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.1875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
